--- a/playwright/test-plans/authenticated/dummy-resources-test-cases.xlsx
+++ b/playwright/test-plans/authenticated/dummy-resources-test-cases.xlsx
@@ -10,11 +10,12 @@
   <sheets>
     <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Client Mapping" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ADO 26191" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Client Mapping" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Client Mapping'!$A$4:$F$52</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$5:$Q$41</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Client Mapping'!$A$4:$F$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$5:$Q$47</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,15 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="540">
   <si>
     <t xml:space="preserve">Dummy Resources (PSD v2) — Test Cases</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: resources/product-specifications-document/AgriERP FSCM - Dummy Resources v2.pdf. Plan: playwright/test-plans/authenticated/dummy-resources.md. Updated 2026-09-30: v2 released on QA, web cases re-verified live (FINDINGS #47–#49); cross-checked against client sheet AgriERP_Dummy_Resource_Test_Cases.xlsx.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend: Change — green = New, yellow = Updated (PSD revision 2026-09-29), white = Existing. Fill in the Result column (Pass / Fail / Blocked / Not Run) when executing. Web results pre-filled from the 2026-09-30 automated run on QA.</t>
+    <t xml:space="preserve">Source: resources/product-specifications-document/AgriERP FSCM - Dummy Resources v2.pdf. Plan: playwright/test-plans/authenticated/dummy-resources.md. Updated 2026-09-30: ADO #26191 impact areas added (DRI-01..06); v2 released on QA, web cases re-verified live (FINDINGS #47–#49); cross-checked against client sheet AgriERP_Dummy_Resource_Test_Cases.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend: Change — green = New, yellow = Updated (PSD revision 2026-09-29), white = Existing. Fill in the Result column (Pass / Fail / Blocked / Not Run) when executing. Results pre-filled from the 2026-09-30 automated runs on QA (web UI + DummyShift API; DRM results cover the server rules, not the mobile screens).</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -91,59 +92,65 @@
     <t xml:space="preserve">DR-01</t>
   </si>
   <si>
-    <t xml:space="preserve">A dummy resource on the WO form takes a No Of Resource headcount</t>
+    <t xml:space="preserve">A dummy resource on the web form takes no quantity (entered on mobile at Start Job)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selecting dummy resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin / Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Functional / Smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager (VBS tenant, QA env). Work Orders → Create New Work Order (Planned) is open with Farm, Operation and Plot set — Add Resources stays inert until all three are set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click '+' → Add Dummy Resource.
+2. Tick a dummy resource and Save.
+3. Look at the resource row and the grid's columns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Operator (DM001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The row is added with the DUMMY RESOURCE badge; the grid has no No Of Resource column and the row has no number input. The quantity is entered on the mobile app when the job starts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figure 1 (p.7) mock; Farm Operations Manager journey steps 3–8 (p.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Automated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrected 2026-09-30: FINDINGS #47 / ADO #26454 withdrawn — the quantity is not a web field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Resources '+' offers Add Resource and Add Dummy Resource</t>
   </si>
   <si>
     <t xml:space="preserve">Existing</t>
   </si>
   <si>
-    <t xml:space="preserve">Selecting dummy resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin / Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Functional / Smoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager (VBS tenant, QA env). Work Orders → Create New Work Order (Planned) is open with Farm, Operation and Plot set — Add Resources stays inert until all three are set.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Add Resources (v2: '+' → Add Dummy Resource; v1 on QA: Select Resources → Dummy Resource switch = Yes).
-2. Tick a dummy resource and confirm.
-3. Look at the resource row on the form.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine Operator (DM001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The row is added under Select Resources with an editable number input under No Of Resource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Solution Overview; Data Dictionary – No. of Resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❌ Expected failure — FINDINGS #47 (no headcount input on web)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Resources '+' offers Add Resource and Add Dummy Resource</t>
-  </si>
-  <si>
     <t xml:space="preserve">P2</t>
   </si>
   <si>
@@ -159,16 +166,10 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Mocks, Figure 1 (p.7)</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ Automated</t>
-  </si>
-  <si>
     <t xml:space="preserve">QA still serves v1 (FINDINGS #34).</t>
   </si>
   <si>
     <t xml:space="preserve">WEB-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass</t>
   </si>
   <si>
     <t xml:space="preserve">DR-03</t>
@@ -242,47 +243,31 @@
     <t xml:space="preserve">DR-06</t>
   </si>
   <si>
-    <t xml:space="preserve">No. of Resources empty or 0 blocks saving</t>
+    <t xml:space="preserve">RETIRED — web save blocked without a quantity</t>
   </si>
   <si>
     <t xml:space="preserve">Validation</t>
   </si>
   <si>
-    <t xml:space="preserve">Negative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave No Of Resource empty and try Submit → Save.
-2. Enter 0 and try again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Of Resource: empty, then 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit is disabled or saving is refused; no 'Saved Successfully' toast.</t>
+    <t xml:space="preserve">Retired 2026-09-30: the quantity is not a web field (Figure 1; Manager journey steps 6–8). The Mandatory Fields rule applies at Start Job and is covered by DRM-04.</t>
   </si>
   <si>
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Validation Rules → Mandatory Fields</t>
   </si>
   <si>
-    <t xml:space="preserve">Automated, @mutating — parked (test.fixme), blocked by FINDINGS #47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSD gives no exact error text; tighten once seen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked</t>
+    <t xml:space="preserve">Retired — see DRM-04 (API)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINDINGS #47 withdrawn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Run</t>
   </si>
   <si>
     <t xml:space="preserve">DR-07</t>
   </si>
   <si>
     <t xml:space="preserve">Dummy resource hours show on web: resource list, Spent Hours, WO logs, Hour Log Adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated</t>
   </si>
   <si>
     <t xml:space="preserve">Hours &amp; integration</t>
@@ -319,9 +304,6 @@
     <t xml:space="preserve">INT-005, INT-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Run</t>
-  </si>
-  <si>
     <t xml:space="preserve">DR-08</t>
   </si>
   <si>
@@ -349,7 +331,10 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Integration with ERP (p.23)</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual (D365)</t>
+    <t xml:space="preserve">Partial: API posting readiness; D365 posting manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API check: GET /api/DummyShift/PostingReadiness/{workOrderId}, /UnpostableResources/{workOrderId}</t>
   </si>
   <si>
     <t xml:space="preserve">INT-001, INT-002, INT-003, INT-004</t>
@@ -362,6 +347,9 @@
   </si>
   <si>
     <t xml:space="preserve">Resource availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative</t>
   </si>
   <si>
     <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager. A named resource is working on a running job (not paused/stopped).</t>
@@ -455,6 +443,9 @@
     <t xml:space="preserve">WEB-004</t>
   </si>
   <si>
+    <t xml:space="preserve">Blocked</t>
+  </si>
+  <si>
     <t xml:space="preserve">DR-12</t>
   </si>
   <si>
@@ -525,6 +516,9 @@
   </si>
   <si>
     <t xml:space="preserve">WEB-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail</t>
   </si>
   <si>
     <t xml:space="preserve">DR-15</t>
@@ -625,12 +619,12 @@
     <t xml:space="preserve">Functional / Positive</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add a dummy resource (DR-01) and enter No Of Resource = 2.
+    <t xml:space="preserve">1. Add a dummy resource (DR-01).
 2. Add no asset.
 3. Submit → Save.</t>
   </si>
   <si>
-    <t xml:space="preserve">Machine Operator (DM001); No Of Resource 2; no asset</t>
+    <t xml:space="preserve">Machine Operator (DM001); no asset</t>
   </si>
   <si>
     <t xml:space="preserve">The WO saves ("Work Order WO-XXXXX | &lt;name&gt; Saved Successfully"); no asset is required.</t>
@@ -639,10 +633,10 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Validation Rules → Mandatory Fields (p.26) — machine and implement attachment is optional</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual — blocked by FINDINGS #47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive counterpart of DR-06.</t>
+    <t xml:space="preserve">✅ Verified manually 2026-09-30 (WO-1393)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-001</t>
   </si>
   <si>
     <t xml:space="preserve">DR-19</t>
@@ -758,6 +752,9 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figure 9 (p.15); Validation Rules – Mandatory Fields</t>
   </si>
   <si>
+    <t xml:space="preserve">✅ Automated (API) — dummy-shifts-api.spec.ts; screens manual</t>
+  </si>
+  <si>
     <t xml:space="preserve">DRM-05</t>
   </si>
   <si>
@@ -782,6 +779,9 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figures 10–12 (p.16–18); Dummy Asset Register</t>
   </si>
   <si>
+    <t xml:space="preserve">API check: GET /api/DummyShift/DummyAssetRegister/{assetType}</t>
+  </si>
+  <si>
     <t xml:space="preserve">BIND-004, BIND-009, VAL-006, VAL-007, VAL-008</t>
   </si>
   <si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figure 13 (p.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API check: POST /api/DummyShift/Preview</t>
   </si>
   <si>
     <t xml:space="preserve">DRM-07</t>
@@ -832,7 +835,7 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figure 14 (p.20); Machine Binding &amp; Shift Window</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ Figure 14 still says 'until Pause or Stop'; the revised Important Point no longer states post-Pause/Stop status. Confirm with PO.</t>
+    <t xml:space="preserve">⚠ Figure 14 still says 'until Pause or Stop'; the revised Important Point no longer states post-Pause/Stop status. Confirm with PO. · API check: POST /api/DummyShift</t>
   </si>
   <si>
     <t xml:space="preserve">BIND-001</t>
@@ -864,6 +867,9 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figure 6 (p.12); Hour Calculation</t>
   </si>
   <si>
+    <t xml:space="preserve">API check: POST /api/DummyShift/Preview; GET /api/DummyShift/PlotSummary/{workOrderId}</t>
+  </si>
+  <si>
     <t xml:space="preserve">VAL-012, VAL-013, VAL-014</t>
   </si>
   <si>
@@ -888,6 +894,9 @@
   </si>
   <si>
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Figures 15–16 (p.21–22); Machine Binding Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API check: POST /api/DummyShift/MachineAvailability</t>
   </si>
   <si>
     <t xml:space="preserve">BIND-002, BIND-003, BIND-010, VAL-002</t>
@@ -919,7 +928,7 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Important Point – Resume Job and Shifts (p.22)</t>
   </si>
   <si>
-    <t xml:space="preserve">PSD was: 'appends a second shift'; now: 'appends a new shift'.</t>
+    <t xml:space="preserve">PSD was: 'appends a second shift'; now: 'appends a new shift'. · API check: POST /api/DummyShift/Resume</t>
   </si>
   <si>
     <t xml:space="preserve">DRM-15</t>
@@ -941,6 +950,9 @@
     <t xml:space="preserve">Plot card reads In Progress before Resume (step 1) and stays In Progress after each Resume (steps 3 and 5). It never returns to To Do between shifts.</t>
   </si>
   <si>
+    <t xml:space="preserve">✅ Automated (API, WO status) — dummy-shifts-api.spec.ts; screens manual</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSD dropped 'only Pause or Stop returns it to To Do'.</t>
   </si>
   <si>
@@ -965,6 +977,9 @@
     <t xml:space="preserve">Shift 1 logs 4 h, Shift 2 logs 2 h; Total Hours Logged shows 6 h resource (plus machine hours). Shift 1 still shows 4 h.</t>
   </si>
   <si>
+    <t xml:space="preserve">API check: GET /api/DummyShift/PlotSummary/{workOrderId}</t>
+  </si>
+  <si>
     <t xml:space="preserve">DRM-17</t>
   </si>
   <si>
@@ -985,6 +1000,9 @@
     <t xml:space="preserve">Both shifts listed on the same plot and day. Shift 1: A × 2, M1, own window. Shift 2: B × 3, M2, own window. Shift 1 unchanged.</t>
   </si>
   <si>
+    <t xml:space="preserve">API check: GET /api/DummyShift/Line/{workOrderLineId}</t>
+  </si>
+  <si>
     <t xml:space="preserve">DRM-11</t>
   </si>
   <si>
@@ -1006,6 +1024,9 @@
   </si>
   <si>
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Headcount Update Validation (p.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API check: PUT /api/DummyShift/Resource/{shiftResourceId}/Headcount</t>
   </si>
   <si>
     <t xml:space="preserve">BIND-005, BIND-006, BIND-007, BIND-008, VAL-003</t>
@@ -1033,6 +1054,9 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Important Point – Correcting and Deleting a Shift (p.22–23)</t>
   </si>
   <si>
+    <t xml:space="preserve">API check: DELETE /api/DummyShift/{shiftId}, /Resource/{shiftResourceId}, /Asset/{shiftAssetId}</t>
+  </si>
+  <si>
     <t xml:space="preserve">VAL-009, VAL-010, VAL-011</t>
   </si>
   <si>
@@ -1059,6 +1083,12 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Named Resource Availability Validation</t>
   </si>
   <si>
+    <t xml:space="preserve">Partial: API covers dummy availability; named half manual — dummy-shifts-api.spec.ts; screens manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API check: POST /api/DummyShift/ResourceAvailability</t>
+  </si>
+  <si>
     <t xml:space="preserve">DRM-14</t>
   </si>
   <si>
@@ -1076,9 +1106,174 @@
     <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — Dummy Resource Audit Trail Logs (p.23)</t>
   </si>
   <si>
+    <t xml:space="preserve">Partial (API): ❌ detach not logged (#50), corrections lack device (#53) — dummy-shifts-api.spec.ts; screens manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API check: GET /api/DummyShift/{shiftId}/Logs, /WorkOrder/{workOrderId}/Logs</t>
+  </si>
+  <si>
     <t xml:space="preserve">AUD-001, AUD-002, AUD-003, AUD-004, AUD-005</t>
   </si>
   <si>
+    <t xml:space="preserve">DRI-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spent Hours unchanged for named and old-style dummy resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact-area regression (ADO 26191)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager (VBS tenant, QA env). One WO with named resources only and hour logs; one pre-v2 WO carrying an old-style (Enh 25942) dummy resource with hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open each WO → Resources table; read Spent Hours.
+2. Click Hours Logged to open the Spent Hours drawer.
+3. Cross-check GET api/WorkOrder/HourLogs for the same WO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WO from `pnpm seed:hourlog`; a pre-v2 dummy WO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spent Hours and the drawer show the same hours as before v2; the API returns the entries (new fields tolerated); old-style dummy hours still shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — ADO 26191 impact 1 — Spent Hours (GET api/WorkOrder/HourLogs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: hour-log-adjustment.spec.ts (named). Old-style dummy: manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRI-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hour log create, edit, void and approve still work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager (VBS tenant, QA env). An In Progress WO (`pnpm seed:hourlog`) with named resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Spent Hours drawer → Create an entry.
+2. Edit it.
+3. Void it.
+4. Approve a pending hour log change request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named resource Agrierp 07 (07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each action succeeds and Spent Hours reflects it; no duplicate or lost entry (index is now non-unique).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — ADO 26191 impact 2 — WorkOrderHourLogs table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: approve/adjust/reject in hour-log-decisions.spec.ts (@mutating). Create/void: manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spent Hours create on a resource with no hours returns 500 — FINDINGS #42.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRI-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal work order still reaches the mobile app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Mobile App as a Supervisor or Machine Operator (VBS tenant, QA env). A normal planned WO (named resources) was just created on web and assigned to the user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create and submit a planned WO on web with named resources.
+2. Refresh the mobile Work Orders list.
+3. Open the WO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any named resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The WO appears with its plots and resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — ADO 26191 impact 3 — WO sync to mobile (ComAX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual (mobile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRI-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Job with named resources only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Mobile App as a Supervisor or Machine Operator (VBS tenant, QA env). A To Do planned WO with named resources only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Swipe a plot card left → Start Job.
+2. Complete the flow without any dummy resource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named resources only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job starts; plot and WO go In Progress; no shift/dummy data is asked for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — ADO 26191 impact 4 — Start Job for normal resources (ComAX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRI-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours split across plots unchanged (Bug 25844)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager (VBS tenant, QA env). A multi-plot WO with named-resource hours, and a dummy shift on one plot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Spent Hours per plot.
+2. Compare the named-resource split with the plots' acreage.
+3. Check the dummy shift's hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two plots of different acreage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named-resource hours are split by acreage as before; shift hours stay on their own plot and are not in the split.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — ADO 26191 impact 5 — Bug 25844 hours distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRI-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old-style dummy resources (Enh 25942) still work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in to the Farm Web App as Admin / Manager (VBS tenant, QA env). A WO created before v2 with a dummy resource and headcount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the WO on web; check the dummy resource row and its headcount.
+2. Check its hours in Spent Hours.
+3. Open it on mobile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-v2 WO with No Of Resource = 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount shown and hours computed from it, on web and mobile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgriERP FSCM - Dummy Resources v2.pdf — ADO 26191 impact 6 — Enh 25942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old-style WOs keep their stored headcount (WO-1391: Dummy Res 04 = 2); new web WOs carry none by design.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Summary</t>
   </si>
   <si>
@@ -1103,6 +1298,108 @@
     <t xml:space="preserve">Open question: the revised PSD no longer states the plot status after Pause or Stop (Figure 14 still says 'until Pause or Stop'). Confirm with the PO before adding a case.</t>
   </si>
   <si>
+    <t xml:space="preserve">ADO #26191 developer note (Mohsin Aqee, 2026-09-29) → test coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: resources/work-items/26191-dummy-resource-v2.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our case(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implemented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shift per plot on Start/Resume Job (crews, headcount, machines, window); many shifts per plot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRM-07, DRM-10, DRM-15, DRM-16, DRM-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated (API)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server calculates hours = headcount × standard hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machines booked for the shift window, no double use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRM-09, DRM-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile corrections: headcount, remove crew, delete shift, attach/detach machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRM-11, DRM-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web API api/DummyShift/* (plot cards, shift list, edit, delete, history, posting checks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRM-04..17, DR-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: dummy-shifts-api.spec.ts (FINDINGS #50–#53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full history log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shifts sync back to Firebase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRM-10 (mobile view)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spent Hours (GET api/WorkOrder/HourLogs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkOrderHourLogs table: create, edit, void, approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WO sync to mobile (ComAX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Job for named resources (ComAX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours distribution across plots (Bug 25844)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old dummy resources (Enh 25942)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Client sheet → this suite (non-mobile tabs only; the client's 'Mobile - Dummy Resource' tab was skipped)</t>
   </si>
   <si>
@@ -1118,12 +1415,6 @@
     <t xml:space="preserve">Client scenario</t>
   </si>
   <si>
-    <t xml:space="preserve">Our case(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coverage</t>
-  </si>
-  <si>
     <t xml:space="preserve">Note</t>
   </si>
   <si>
@@ -1238,9 +1529,6 @@
     <t xml:space="preserve">Headcount increase re-validates the machine only over the newly claimed (extra) time</t>
   </si>
   <si>
-    <t xml:space="preserve">Partial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Re-check limited to the extra time isn't asserted separately. Mobile, not added.</t>
   </si>
   <si>
@@ -1277,133 +1565,133 @@
     <t xml:space="preserve">No. of Resources is mandatory and must be greater than zero (Web &amp; Mobile)</t>
   </si>
   <si>
-    <t xml:space="preserve">DR-06, DRM-04, DR-18</t>
+    <t xml:space="preserve">DRM-04, DR-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The quantity is a mobile field: enforced at Start Job (DRM-04, API). 'Attachment optional' clause: DR-18. DR-06 retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine already bound for any part of a shift window cannot be selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount increase is re-validated and blocked on conflict with an actual resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A named resource already on a running job cannot be selected again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR-09, DRM-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy resources are never blocked by a running job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Machine / Add Dummy Machine choice is shown only when the register holds a dummy asset of that kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selection page opens directly when the register holds no dummy asset of that kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both dummy and named resources may select from either asset register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deleting a shift removes its hours and machine bindings from the plot total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removing the last resource of a shift deletes the shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shift/resource deletion is blocked once the work order is completed and hours are posted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours logged equal No. of Resources × Standard Hours and are read-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine/implement hours equal the hours of the resource they are attached to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAL-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plot total equals the sum of resource hours and machine/implement hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy resource hours post to the ERP project like a named resource's hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posting is restricted when the work order/plot has no ERP project linkage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrections made before completion are re-posted to ERP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours become read-only after work order completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System-generated dummy resource logs appear on Hour Log Adjustment with headcount and standard hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy resource hours are visible with source, device, and user on Web resource list, Spent Hours, and WO logs</t>
   </si>
   <si>
     <t xml:space="preserve">Extended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Attachment optional' clause added as DR-18. Web half blocked: no headcount input (FINDINGS #47).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine already bound for any part of a shift window cannot be selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Headcount increase is re-validated and blocked on conflict with an actual resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A named resource already on a running job cannot be selected again</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR-09, DRM-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dummy resources are never blocked by a running job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add Machine / Add Dummy Machine choice is shown only when the register holds a dummy asset of that kind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selection page opens directly when the register holds no dummy asset of that kind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both dummy and named resources may select from either asset register</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deleting a shift removes its hours and machine bindings from the plot total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Removing the last resource of a shift deletes the shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shift/resource deletion is blocked once the work order is completed and hours are posted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours logged equal No. of Resources × Standard Hours and are read-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine/implement hours equal the hours of the resource they are attached to</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAL-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plot total equals the sum of resource hours and machine/implement hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dummy resource hours post to the ERP project like a named resource's hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posting is restricted when the work order/plot has no ERP project linkage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrections made before completion are re-posted to ERP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours become read-only after work order completion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System-generated dummy resource logs appear on Hour Log Adjustment with headcount and standard hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dummy resource hours are visible with source, device, and user on Web resource list, Spent Hours, and WO logs</t>
   </si>
   <si>
     <t xml:space="preserve">DR-07 now also checks the work order logs.</t>
@@ -1558,8 +1846,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1570,8 +1858,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2018,7 +2306,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2151,23 +2439,25 @@
       <c r="N6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="P6" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+        <v>38</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>23</v>
@@ -2179,37 +2469,37 @@
         <v>25</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2219,8 +2509,8 @@
       <c r="B8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
+      <c r="C8" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>23</v>
@@ -2232,10 +2522,10 @@
         <v>25</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>28</v>
@@ -2244,7 +2534,7 @@
         <v>49</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>50</v>
@@ -2253,14 +2543,14 @@
         <v>51</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="s">
         <v>52</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2270,8 +2560,8 @@
       <c r="B9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>23</v>
@@ -2283,7 +2573,7 @@
         <v>25</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
@@ -2295,7 +2585,7 @@
         <v>56</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>57</v>
@@ -2304,14 +2594,14 @@
         <v>58</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="s">
         <v>59</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,8 +2611,8 @@
       <c r="B10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
+      <c r="C10" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>23</v>
@@ -2355,17 +2645,17 @@
         <v>67</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="s">
         <v>68</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>69</v>
       </c>
@@ -2385,51 +2675,51 @@
         <v>25</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="M11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="N11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="O11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="P11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>24</v>
@@ -2438,102 +2728,104 @@
         <v>25</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="N12" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="O12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="P12" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="L12" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="Q12" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
+        <v>90</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="O13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="P13" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="Q13" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
+        <v>101</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>24</v>
@@ -2542,49 +2834,49 @@
         <v>25</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="N14" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>24</v>
@@ -2596,45 +2888,45 @@
         <v>26</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="M15" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="N15" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="O15" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="L15" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="P15" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>23</v>
@@ -2646,46 +2938,46 @@
         <v>25</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="N16" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="O16" s="5"/>
       <c r="P16" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>23</v>
@@ -2700,43 +2992,43 @@
         <v>62</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J17" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="M17" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="N17" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O17" s="5"/>
       <c r="P17" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>23</v>
@@ -2751,43 +3043,43 @@
         <v>62</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J18" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N18" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>23</v>
@@ -2802,45 +3094,45 @@
         <v>62</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J19" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N19" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="O19" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="P19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="M19" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="N19" s="5" t="s">
+      <c r="Q19" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>23</v>
@@ -2855,43 +3147,43 @@
         <v>26</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J20" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L20" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="M20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="N20" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="O20" s="5"/>
       <c r="P20" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>23</v>
@@ -2903,51 +3195,51 @@
         <v>25</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I21" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="L21" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="M21" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="O21" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="N21" s="5" t="s">
+      <c r="P21" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="O21" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="Q21" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>24</v>
@@ -2959,45 +3251,45 @@
         <v>26</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I22" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="L22" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="M22" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="N22" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="O22" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="N22" s="5" t="s">
+      <c r="P22" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="O22" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>184</v>
-      </c>
       <c r="Q22" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>71</v>
@@ -3009,48 +3301,46 @@
         <v>25</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J23" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="M23" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="N23" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="O23" s="5"/>
+      <c r="P23" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="N23" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="Q23" s="7" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>23</v>
@@ -3071,99 +3361,99 @@
         <v>64</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>67</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="G25" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>63</v>
       </c>
       <c r="I25" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="M25" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="5" t="s">
+      <c r="N25" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="O25" s="5"/>
       <c r="P25" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>22</v>
+        <v>209</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>62</v>
@@ -3172,182 +3462,184 @@
         <v>63</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="M26" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="N26" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O26" s="5"/>
       <c r="P26" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="K27" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="L27" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="M27" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="L27" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>221</v>
-      </c>
       <c r="N27" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O27" s="5"/>
       <c r="P27" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>22</v>
+        <v>221</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="L28" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="M28" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="N28" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="5" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="K29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="L29" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="M29" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="M29" s="5" t="s">
+      <c r="N29" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="O29" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="N29" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O29" s="5"/>
       <c r="P29" s="5" t="s">
         <v>236</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3357,23 +3649,23 @@
       <c r="B30" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>22</v>
+      <c r="C30" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="G30" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>239</v>
@@ -3391,397 +3683,407 @@
         <v>243</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O30" s="5"/>
+        <v>207</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="P30" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>22</v>
+        <v>246</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>22</v>
+        <v>256</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O32" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>263</v>
+      </c>
       <c r="P32" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>22</v>
+        <v>266</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>272</v>
+      </c>
       <c r="P33" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>83</v>
+        <v>275</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O36" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="P36" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O37" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="P37" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>22</v>
+        <v>304</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>26</v>
@@ -3790,188 +4092,506 @@
         <v>55</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O38" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="P38" s="5" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>22</v>
+        <v>313</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O39" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>318</v>
+      </c>
       <c r="P39" s="5" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>22</v>
+        <v>321</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O40" s="5"/>
+        <v>327</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="P40" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>22</v>
+        <v>330</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O41" s="5"/>
+        <v>334</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>335</v>
+      </c>
       <c r="P41" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>94</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q46" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="N47" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q47" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q41"/>
+  <autoFilter ref="A5:Q47"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q6:Q41" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q6:Q47" type="list">
       <formula1>"Pass,Fail,Blocked,Not Run"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4001,59 +4621,59 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>326</v>
+        <v>387</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B4" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$C$6:$C$41,"New")</f>
-        <v>13</v>
+        <f aca="false">COUNTIF('Test Cases'!$C$6:$C$47,"New")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B5" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$C$6:$C$41,"Updated")</f>
-        <v>2</v>
+        <f aca="false">COUNTIF('Test Cases'!$C$6:$C$47,"Updated")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B6" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$C$6:$C$41,"Existing")</f>
-        <v>21</v>
+        <f aca="false">COUNTIF('Test Cases'!$C$6:$C$47,"Existing")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">SUM(B4:B6)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>329</v>
+        <v>390</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,43 +4681,43 @@
         <v>25</v>
       </c>
       <c r="B10" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$F$6:$F$41,"Web")</f>
-        <v>18</v>
+        <f aca="false">COUNTIF('Test Cases'!$F$6:$F$47,"Web")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B11" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$F$6:$F$41,"Mobile")</f>
-        <v>17</v>
+        <f aca="false">COUNTIF('Test Cases'!$F$6:$F$47,"Mobile")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B12" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$F$6:$F$41,"Web / D365")</f>
+        <f aca="false">COUNTIF('Test Cases'!$F$6:$F$47,"Web / D365")</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">SUM(B10:B12)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>330</v>
+        <v>391</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4105,17 +4725,17 @@
         <v>26</v>
       </c>
       <c r="B16" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$G$6:$G$41,"P1")</f>
-        <v>13</v>
+        <f aca="false">COUNTIF('Test Cases'!$G$6:$G$47,"P1")</f>
+        <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$G$6:$G$41,"P2")</f>
-        <v>17</v>
+        <f aca="false">COUNTIF('Test Cases'!$G$6:$G$47,"P2")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4123,75 +4743,75 @@
         <v>62</v>
       </c>
       <c r="B18" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$G$6:$G$41,"P3")</f>
-        <v>6</v>
+        <f aca="false">COUNTIF('Test Cases'!$G$6:$G$47,"P3")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="B19" s="10" t="n">
         <f aca="false">SUM(B16:B18)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>331</v>
+        <v>392</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B22" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$41,"Pass")</f>
-        <v>6</v>
+        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$47,"Pass")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B23" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$41,"Fail")</f>
+        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$47,"Fail")</f>
         <v>3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="B24" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$41,"Blocked")</f>
-        <v>4</v>
+        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$47,"Blocked")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B25" s="11" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$41,"Not Run")</f>
-        <v>23</v>
+        <f aca="false">COUNTIF('Test Cases'!$Q$6:$Q$47,"Not Run")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">SUM(B22:B25)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>332</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4206,6 +4826,237 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4223,162 +5074,162 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>334</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>335</v>
+        <v>430</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>336</v>
+        <v>431</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>337</v>
+        <v>432</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>340</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>342</v>
+        <v>435</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>343</v>
+        <v>37</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>344</v>
+        <v>437</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>345</v>
+        <v>438</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>343</v>
+      <c r="E6" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>347</v>
+        <v>440</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>343</v>
+        <v>441</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>349</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>350</v>
+        <v>443</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>352</v>
+        <v>445</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>353</v>
+        <v>446</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>354</v>
+        <v>447</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>355</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4386,784 +5237,784 @@
         <v>68</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>356</v>
+        <v>449</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>343</v>
+      <c r="E12" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>357</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>358</v>
+        <v>451</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>359</v>
+        <v>452</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>343</v>
+      <c r="E13" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>360</v>
+        <v>453</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>361</v>
+        <v>454</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>343</v>
+        <v>441</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>363</v>
+        <v>456</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>364</v>
+        <v>457</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>366</v>
+        <v>459</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>368</v>
+        <v>461</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>343</v>
+        <v>265</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>369</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>370</v>
+        <v>463</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>371</v>
+        <v>464</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>343</v>
+        <v>265</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>372</v>
+        <v>465</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>373</v>
+        <v>466</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>343</v>
+        <v>228</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>374</v>
+        <v>467</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>375</v>
+        <v>468</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>343</v>
+        <v>303</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>376</v>
+        <v>469</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>377</v>
+        <v>470</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>379</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>380</v>
+        <v>472</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>381</v>
+        <v>473</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>343</v>
+        <v>303</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>382</v>
+        <v>474</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>383</v>
+        <v>475</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>343</v>
+        <v>303</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>384</v>
+        <v>476</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>385</v>
+        <v>477</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>343</v>
+        <v>228</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>386</v>
+        <v>478</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>387</v>
+        <v>479</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>388</v>
+        <v>480</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>390</v>
+        <v>482</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>391</v>
+        <v>483</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>393</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>394</v>
+        <v>485</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>395</v>
+        <v>486</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>343</v>
+        <v>265</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>396</v>
+        <v>487</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>343</v>
+        <v>303</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>398</v>
+        <v>489</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>399</v>
+        <v>490</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>343</v>
+        <v>491</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>401</v>
+        <v>492</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>402</v>
+        <v>493</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>343</v>
+        <v>491</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>403</v>
+        <v>494</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>404</v>
+        <v>495</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>343</v>
+        <v>228</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>405</v>
+        <v>496</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>406</v>
+        <v>497</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>343</v>
+        <v>228</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>407</v>
+        <v>498</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>408</v>
+        <v>499</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>343</v>
+        <v>228</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>409</v>
+        <v>500</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>410</v>
+        <v>501</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>343</v>
+        <v>312</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>411</v>
+        <v>502</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>412</v>
+        <v>503</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>343</v>
+        <v>312</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>413</v>
+        <v>504</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>414</v>
+        <v>505</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>343</v>
+        <v>312</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>415</v>
+        <v>506</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>416</v>
+        <v>507</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>343</v>
+        <v>255</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>417</v>
+        <v>508</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>418</v>
+        <v>509</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>343</v>
+        <v>255</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>419</v>
+        <v>510</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>389</v>
+        <v>481</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>420</v>
+        <v>511</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>343</v>
+        <v>255</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>421</v>
+        <v>512</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>423</v>
+        <v>514</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>343</v>
+        <v>89</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>425</v>
+        <v>516</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>343</v>
+        <v>89</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>426</v>
+        <v>517</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>427</v>
+        <v>518</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>343</v>
+        <v>89</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>428</v>
+        <v>519</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>429</v>
+        <v>520</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>343</v>
+        <v>89</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>430</v>
+        <v>521</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>431</v>
+        <v>522</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>343</v>
+        <v>77</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>432</v>
+        <v>523</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>433</v>
+        <v>524</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>392</v>
+        <v>77</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>525</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>434</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>435</v>
+        <v>527</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="F47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>436</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="F48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>439</v>
+        <v>531</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>343</v>
+        <v>329</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>441</v>
+        <v>533</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>442</v>
+        <v>534</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>343</v>
+        <v>329</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>443</v>
+        <v>535</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>343</v>
+        <v>329</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="F51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>445</v>
+        <v>537</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>446</v>
+        <v>538</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>447</v>
+        <v>539</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="B55" s="11" t="n">
         <f aca="false">COUNTIF($E$5:$E$52,"Covered")</f>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>392</v>
+        <v>525</v>
       </c>
       <c r="B56" s="11" t="n">
         <f aca="false">COUNTIF($E$5:$E$52,"Extended")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="B57" s="11" t="n">
         <f aca="false">COUNTIF($E$5:$E$52,"Added")</f>
@@ -5172,7 +6023,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="B58" s="11" t="n">
         <f aca="false">COUNTIF($E$5:$E$52,"Partial")</f>
@@ -5181,7 +6032,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="B59" s="10" t="n">
         <f aca="false">SUM(B55:B58)</f>
